--- a/output/pdf_financials_xlsx/CTG.xlsx
+++ b/output/pdf_financials_xlsx/CTG.xlsx
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.052132</v>
+        <v>-0.052132</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.034502</v>
+        <v>-0.034502</v>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.052132</v>
+        <v>-0.052132</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.034502</v>
+        <v>-0.034502</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.052132</v>
+        <v>-0.052132</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.034502</v>
+        <v>-0.034502</v>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2.6066</v>
+        <v>-2.6066</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.052132</v>
+        <v>-0.052132</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.034502</v>
+        <v>-0.034502</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.052132</v>
+        <v>-0.052132</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.034502</v>
+        <v>-0.034502</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.040475</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.040475</v>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
@@ -5142,25 +5142,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.040475</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.040475</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.040475</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.040475</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.040475</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.040475</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.040475</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>0.35839</v>
@@ -9532,7 +9532,11 @@
           <t>Share-based payments reserve (Note 4)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -9926,7 +9930,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -18529,10 +18537,10 @@
         </is>
       </c>
       <c r="F137" s="5" t="n">
-        <v>0.052132</v>
+        <v>-0.052132</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.034502</v>
+        <v>-0.034502</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CTG.xlsx
+++ b/output/pdf_financials_xlsx/CTG.xlsx
@@ -978,10 +978,10 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.00164</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
     </row>
     <row r="13">
@@ -1788,10 +1788,10 @@
         <v>-0.08749</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.336748</v>
+        <v>-1.338388</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.312152</v>
+        <v>-0.312154</v>
       </c>
     </row>
     <row r="28">
@@ -1888,10 +1888,10 @@
         <v>-0.08749</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.335756</v>
+        <v>-1.337396</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.312152</v>
+        <v>-0.312154</v>
       </c>
     </row>
     <row r="30">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.06528100000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.028643</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -2118,25 +2118,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.117296</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.060366</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.064272</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.038052</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.010573</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.466105</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.381062</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.003653</v>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.06528100000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.028643</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -2218,25 +2218,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.117296</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.060366</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.064272</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.038052</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.010573</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.466105</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.381062</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.003653</v>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -17632,7 +17632,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">

--- a/output/pdf_financials_xlsx/CTG.xlsx
+++ b/output/pdf_financials_xlsx/CTG.xlsx
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="M120" s="3" t="n">
-        <v>0</v>
+        <v>0.048718</v>
       </c>
       <c r="N120" s="3" t="n">
         <v>0</v>
@@ -11159,7 +11159,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
